--- a/extenbooks/ES2201_extenbook.xlsx
+++ b/extenbooks/ES2201_extenbook.xlsx
@@ -2838,7 +2838,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A141"/>
+  <dimension ref="A1:A172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2898,7 +2898,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>**Status**: ingested</t>
+          <t>**Status**: study_complete</t>
         </is>
       </c>
     </row>
@@ -3677,6 +3677,211 @@
       <c r="A141" t="inlineStr">
         <is>
           <t>None. v1.0 is verbatim transcription.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>## 6. Conceptual continuity vs adjacent concepts</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>The extension proxy (IRS SOI Pub 1304 Tables 1.4 and 1, re-fitted per</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>year using MLE) measures `two-class econophysics income distribution</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>parameters (G', ⟨r⟩, ⟨w⟩, f, α)` rather than `Gini coefficient on full</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>AGI distribution` or `top-10% income share (Piketty-Saez)` because:</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>- Source agency choice: IRS SOI Pub 1304 is the only US administrative</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  micro-data binned-tabulation source that supports the</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Dragulescu-Yakovenko exponential + Pareto MLE jointly. Survey-based</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CPS/PSID sources truncate the Pareto top tail and are not suitable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>- Methodology continuity: paper-window 2002-2016 parameters were MLE-fit</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  on SOI bin midpoints; extension years (2017+) re-fit on the same Tables</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  1.4 + 1, NOT growth-rate-spliced from the existing fitted parameters</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  (per Anu Framework No Lazy Splices rule, since these five parameters</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  are jointly estimated, not directly observed).</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>- Disambiguation: G' is the *bottom-97%* Gini, NOT the full-population</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Gini (Census/CBO/World Bank report the latter); α is the *top-3%*</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Pareto exponent, NOT the Piketty-Saez top-share statistic; ⟨w⟩ is a</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  regression-derived "income temperature" inverse slope, NOT a sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  mean.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>The book's original concept (Shaikh-Jacobo 2020 p. 5, Table 1) was:</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>"the parameters of the two-class income distribution model" estimated</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>under the universal-arbitrage interpretation. The modern series</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>preserves the five-parameter joint-MLE estimator and the bottom-97% /</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>top-3% split-point convention while permitting TCJA/CARES AGI definition</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>revisions in 2017+ to introduce documented methodological breaks. This</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>is NOT a proxy substitution forbidden by the No-Proxy rule because</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>IRS SOI Pub 1304 is exactly the data the paper uses; extension reruns</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>the paper's MLE estimator on later vintages of the same publication.</t>
         </is>
       </c>
     </row>
@@ -4168,11 +4373,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4195,54 +4400,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>phases_completed</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>[5, 6, 7]</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>artifacts</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>{"dpr": "Technical/docs/series/ES2201_DPR.md", "epr": "Technical/docs/series/ES2201_EPR.md", "loader": "Technical/code/L01_loaders/L01_ES2201_load.py", "processor": "Technical/code/P02_processors/P02_ES2201_construct.py", "validator": "Technical/code/V03_validators/V03_ES2201_validate.py"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>last_updated</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>author</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>opus-fanout-ES</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
